--- a/19/1 Excel/Advance Formulas and Functions/Advance Formula and Functions-2.xlsx
+++ b/19/1 Excel/Advance Formulas and Functions/Advance Formula and Functions-2.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" firstSheet="3" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" firstSheet="5" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Flash Fill" sheetId="21" state="hidden" r:id="rId1"/>
